--- a/project/sample-imports/patients-uat.xlsx
+++ b/project/sample-imports/patients-uat.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>file_number</t>
   </si>
@@ -37,42 +37,6 @@
     <t>mobile</t>
   </si>
   <si>
-    <t>medical_aid_provider</t>
-  </si>
-  <si>
-    <t>medical_aid_plan</t>
-  </si>
-  <si>
-    <t>medical_aid_member_number</t>
-  </si>
-  <si>
-    <t>emergency_contact_name</t>
-  </si>
-  <si>
-    <t>emergency_contact_phone</t>
-  </si>
-  <si>
-    <t>emergency_contact_relationship</t>
-  </si>
-  <si>
-    <t>blood_type</t>
-  </si>
-  <si>
-    <t>allergies</t>
-  </si>
-  <si>
-    <t>chronic_conditions</t>
-  </si>
-  <si>
-    <t>current_medications</t>
-  </si>
-  <si>
-    <t>referring_doctor</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
     <t>UAT-P-001</t>
   </si>
   <si>
@@ -97,42 +61,6 @@
     <t>0825550001</t>
   </si>
   <si>
-    <t>Discovery Health</t>
-  </si>
-  <si>
-    <t>Classic Saver</t>
-  </si>
-  <si>
-    <t>900100123</t>
-  </si>
-  <si>
-    <t>Sibusiso Nkosi</t>
-  </si>
-  <si>
-    <t>0829001001</t>
-  </si>
-  <si>
-    <t>Husband</t>
-  </si>
-  <si>
-    <t>O+</t>
-  </si>
-  <si>
-    <t>Penicillin;Latex</t>
-  </si>
-  <si>
-    <t>Asthma</t>
-  </si>
-  <si>
-    <t>Ventolin</t>
-  </si>
-  <si>
-    <t>Dr A Naidoo</t>
-  </si>
-  <si>
-    <t>Prefers morning appointments</t>
-  </si>
-  <si>
     <t>UAT-P-002</t>
   </si>
   <si>
@@ -157,42 +85,6 @@
     <t>0825550002</t>
   </si>
   <si>
-    <t>Bonitas</t>
-  </si>
-  <si>
-    <t>BonComprehensive</t>
-  </si>
-  <si>
-    <t>BN4455210</t>
-  </si>
-  <si>
-    <t>Nomvula Dube</t>
-  </si>
-  <si>
-    <t>0829001002</t>
-  </si>
-  <si>
-    <t>Wife</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>Sulfa drugs</t>
-  </si>
-  <si>
-    <t>Hypertension;Type 2 diabetes</t>
-  </si>
-  <si>
-    <t>Amlodipine;Metformin</t>
-  </si>
-  <si>
-    <t>Dr P Govender</t>
-  </si>
-  <si>
-    <t>Diabetic review every 3 months</t>
-  </si>
-  <si>
     <t>UAT-P-003</t>
   </si>
   <si>
@@ -214,36 +106,6 @@
     <t>0825550003</t>
   </si>
   <si>
-    <t>Momentum Health</t>
-  </si>
-  <si>
-    <t>Ingwe</t>
-  </si>
-  <si>
-    <t>MM7788341</t>
-  </si>
-  <si>
-    <t>Palesa Molefe</t>
-  </si>
-  <si>
-    <t>0829001003</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>B-</t>
-  </si>
-  <si>
-    <t>Peanuts</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Pregnant, 2nd trimester</t>
-  </si>
-  <si>
     <t>UAT-P-004</t>
   </si>
   <si>
@@ -265,30 +127,6 @@
     <t>0825550004</t>
   </si>
   <si>
-    <t>Hendrik van Wyk</t>
-  </si>
-  <si>
-    <t>0829001004</t>
-  </si>
-  <si>
-    <t>Son</t>
-  </si>
-  <si>
-    <t>AB+</t>
-  </si>
-  <si>
-    <t>Arthritis;High cholesterol</t>
-  </si>
-  <si>
-    <t>Atorvastatin;Celebrex</t>
-  </si>
-  <si>
-    <t>Dr S Pillay</t>
-  </si>
-  <si>
-    <t>Self-funded patient</t>
-  </si>
-  <si>
     <t>UAT-P-005</t>
   </si>
   <si>
@@ -308,42 +146,6 @@
   </si>
   <si>
     <t>0825550005</t>
-  </si>
-  <si>
-    <t>GEMS</t>
-  </si>
-  <si>
-    <t>Sapphire</t>
-  </si>
-  <si>
-    <t>GM2200987</t>
-  </si>
-  <si>
-    <t>Thabo Khumalo</t>
-  </si>
-  <si>
-    <t>0829001005</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>O-</t>
-  </si>
-  <si>
-    <t>Aspirin;Shellfish</t>
-  </si>
-  <si>
-    <t>Epilepsy</t>
-  </si>
-  <si>
-    <t>Epilim</t>
-  </si>
-  <si>
-    <t>Dr L Mahlangu</t>
-  </si>
-  <si>
-    <t>Student, evening slots only</t>
   </si>
 </sst>
 </file>
@@ -720,10 +522,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -748,351 +550,135 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="H5" t="s">
         <v>37</v>
       </c>
-      <c r="S2" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>38</v>
       </c>
-      <c r="T2" t="s">
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C6" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D6" t="s">
         <v>41</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E6" t="s">
         <v>42</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F6" t="s">
         <v>43</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
         <v>44</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" t="s">
-        <v>54</v>
-      </c>
-      <c r="P3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>56</v>
-      </c>
-      <c r="R3" t="s">
-        <v>57</v>
-      </c>
-      <c r="S3" t="s">
-        <v>58</v>
-      </c>
-      <c r="T3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L4" t="s">
-        <v>70</v>
-      </c>
-      <c r="M4" t="s">
-        <v>71</v>
-      </c>
-      <c r="N4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" t="s">
-        <v>73</v>
-      </c>
-      <c r="P4" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>75</v>
-      </c>
-      <c r="R4" t="s">
-        <v>75</v>
-      </c>
-      <c r="S4" t="s">
-        <v>75</v>
-      </c>
-      <c r="T4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I5" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L5" t="s">
-        <v>84</v>
-      </c>
-      <c r="M5" t="s">
-        <v>85</v>
-      </c>
-      <c r="N5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O5" t="s">
-        <v>87</v>
-      </c>
-      <c r="P5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>88</v>
-      </c>
-      <c r="R5" t="s">
-        <v>89</v>
-      </c>
-      <c r="S5" t="s">
-        <v>90</v>
-      </c>
-      <c r="T5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>98</v>
-      </c>
-      <c r="I6" t="s">
-        <v>99</v>
-      </c>
-      <c r="J6" t="s">
-        <v>100</v>
-      </c>
-      <c r="K6" t="s">
-        <v>101</v>
-      </c>
-      <c r="L6" t="s">
-        <v>102</v>
-      </c>
-      <c r="M6" t="s">
-        <v>103</v>
-      </c>
-      <c r="N6" t="s">
-        <v>104</v>
-      </c>
-      <c r="O6" t="s">
-        <v>105</v>
-      </c>
-      <c r="P6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>107</v>
-      </c>
-      <c r="R6" t="s">
-        <v>108</v>
-      </c>
-      <c r="S6" t="s">
-        <v>109</v>
-      </c>
-      <c r="T6" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
